--- a/Thesis/Checklist.xlsx
+++ b/Thesis/Checklist.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\benel\Coding\Python\Thesis\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B1285F5-67E9-4DE8-8602-AD8977606479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,10 +24,92 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="23">
+  <si>
+    <t>MODEL</t>
+  </si>
+  <si>
+    <t>xgb</t>
+  </si>
+  <si>
+    <t>equal</t>
+  </si>
+  <si>
+    <t>hrp</t>
+  </si>
+  <si>
+    <t>lstm</t>
+  </si>
+  <si>
+    <t>mcap</t>
+  </si>
+  <si>
+    <t>mvo</t>
+  </si>
+  <si>
+    <t>rf</t>
+  </si>
+  <si>
+    <t>sp500</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>hmm</t>
+  </si>
+  <si>
+    <t>wasserstein</t>
+  </si>
+  <si>
+    <t>changepoint</t>
+  </si>
+  <si>
+    <t>pooled</t>
+  </si>
+  <si>
+    <t>monthly</t>
+  </si>
+  <si>
+    <t>quarterly</t>
+  </si>
+  <si>
+    <t>yearly</t>
+  </si>
+  <si>
+    <t>TC</t>
+  </si>
+  <si>
+    <t>REGIME</t>
+  </si>
+  <si>
+    <t>MOMENT</t>
+  </si>
+  <si>
+    <t>REGIME_RISK</t>
+  </si>
+  <si>
+    <t>FREQ</t>
+  </si>
+  <si>
+    <t>STATUS</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -49,8 +137,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -66,6 +168,23 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<FeaturePropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <bag type="Checkbox"/>
+  <bag type="XFControls">
+    <bagId k="CellControl">0</bagId>
+  </bag>
+  <bag type="XFComplement">
+    <bagId k="XFControls">1</bagId>
+  </bag>
+  <bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <a k="MappedFeaturePropertyBags">
+      <bagId>2</bagId>
+    </a>
+  </bag>
+</FeaturePropertyBags>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -330,10 +449,1774 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="C3:U43"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="3.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="T3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="U3" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0</v>
+      </c>
+      <c r="K4" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" t="s">
+        <v>13</v>
+      </c>
+      <c r="M4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>15</v>
+      </c>
+      <c r="O4" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>9</v>
+      </c>
+      <c r="R4" t="s">
+        <v>13</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="s">
+        <v>16</v>
+      </c>
+      <c r="U4" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2">
+        <v>0</v>
+      </c>
+      <c r="K5" t="s">
+        <v>10</v>
+      </c>
+      <c r="L5" t="s">
+        <v>13</v>
+      </c>
+      <c r="M5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N5" t="s">
+        <v>15</v>
+      </c>
+      <c r="O5" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P5" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>10</v>
+      </c>
+      <c r="R5" t="s">
+        <v>13</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="s">
+        <v>16</v>
+      </c>
+      <c r="U5" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0</v>
+      </c>
+      <c r="K6" t="s">
+        <v>11</v>
+      </c>
+      <c r="L6" t="s">
+        <v>13</v>
+      </c>
+      <c r="M6" t="b">
+        <v>1</v>
+      </c>
+      <c r="N6" t="s">
+        <v>15</v>
+      </c>
+      <c r="O6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P6" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>11</v>
+      </c>
+      <c r="R6" t="s">
+        <v>13</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="s">
+        <v>16</v>
+      </c>
+      <c r="U6" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0</v>
+      </c>
+      <c r="K7" t="s">
+        <v>12</v>
+      </c>
+      <c r="L7" t="s">
+        <v>13</v>
+      </c>
+      <c r="M7" t="b">
+        <v>1</v>
+      </c>
+      <c r="N7" t="s">
+        <v>15</v>
+      </c>
+      <c r="O7" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P7" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>12</v>
+      </c>
+      <c r="R7" t="s">
+        <v>13</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="s">
+        <v>16</v>
+      </c>
+      <c r="U7" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="2">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2">
+        <v>10</v>
+      </c>
+      <c r="K8" t="s">
+        <v>9</v>
+      </c>
+      <c r="L8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M8" t="b">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>15</v>
+      </c>
+      <c r="O8" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P8" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>9</v>
+      </c>
+      <c r="R8" t="s">
+        <v>13</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="s">
+        <v>16</v>
+      </c>
+      <c r="U8" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C9" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="2">
+        <v>10</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2">
+        <v>10</v>
+      </c>
+      <c r="K9" t="s">
+        <v>10</v>
+      </c>
+      <c r="L9" t="s">
+        <v>13</v>
+      </c>
+      <c r="M9" t="b">
+        <v>1</v>
+      </c>
+      <c r="N9" t="s">
+        <v>15</v>
+      </c>
+      <c r="O9" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>10</v>
+      </c>
+      <c r="R9" t="s">
+        <v>13</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="s">
+        <v>16</v>
+      </c>
+      <c r="U9" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="2">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I10" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" s="2">
+        <v>10</v>
+      </c>
+      <c r="K10" t="s">
+        <v>11</v>
+      </c>
+      <c r="L10" t="s">
+        <v>13</v>
+      </c>
+      <c r="M10" t="b">
+        <v>1</v>
+      </c>
+      <c r="N10" t="s">
+        <v>15</v>
+      </c>
+      <c r="O10" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>11</v>
+      </c>
+      <c r="R10" t="s">
+        <v>13</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="s">
+        <v>16</v>
+      </c>
+      <c r="U10" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="2">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" s="2">
+        <v>10</v>
+      </c>
+      <c r="K11" t="s">
+        <v>12</v>
+      </c>
+      <c r="L11" t="s">
+        <v>13</v>
+      </c>
+      <c r="M11" t="b">
+        <v>1</v>
+      </c>
+      <c r="N11" t="s">
+        <v>15</v>
+      </c>
+      <c r="O11" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>12</v>
+      </c>
+      <c r="R11" t="s">
+        <v>13</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="s">
+        <v>16</v>
+      </c>
+      <c r="U11" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C12" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="2">
+        <v>20</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" t="s">
+        <v>14</v>
+      </c>
+      <c r="I12" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" s="2">
+        <v>20</v>
+      </c>
+      <c r="K12" t="s">
+        <v>9</v>
+      </c>
+      <c r="L12" t="s">
+        <v>13</v>
+      </c>
+      <c r="M12" t="b">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>15</v>
+      </c>
+      <c r="O12" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P12" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>9</v>
+      </c>
+      <c r="R12" t="s">
+        <v>13</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="s">
+        <v>16</v>
+      </c>
+      <c r="U12" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="2">
+        <v>20</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" s="2">
+        <v>20</v>
+      </c>
+      <c r="K13" t="s">
+        <v>10</v>
+      </c>
+      <c r="L13" t="s">
+        <v>13</v>
+      </c>
+      <c r="M13" t="b">
+        <v>1</v>
+      </c>
+      <c r="N13" t="s">
+        <v>15</v>
+      </c>
+      <c r="O13" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P13" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>10</v>
+      </c>
+      <c r="R13" t="s">
+        <v>13</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="s">
+        <v>16</v>
+      </c>
+      <c r="U13" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C14" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="2">
+        <v>20</v>
+      </c>
+      <c r="E14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" t="s">
+        <v>14</v>
+      </c>
+      <c r="I14" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" s="2">
+        <v>20</v>
+      </c>
+      <c r="K14" t="s">
+        <v>11</v>
+      </c>
+      <c r="L14" t="s">
+        <v>13</v>
+      </c>
+      <c r="M14" t="b">
+        <v>1</v>
+      </c>
+      <c r="N14" t="s">
+        <v>15</v>
+      </c>
+      <c r="O14" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P14" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>11</v>
+      </c>
+      <c r="R14" t="s">
+        <v>13</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="s">
+        <v>16</v>
+      </c>
+      <c r="U14" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="2">
+        <v>20</v>
+      </c>
+      <c r="E15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" t="s">
+        <v>14</v>
+      </c>
+      <c r="I15" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2">
+        <v>20</v>
+      </c>
+      <c r="K15" t="s">
+        <v>12</v>
+      </c>
+      <c r="L15" t="s">
+        <v>13</v>
+      </c>
+      <c r="M15" t="b">
+        <v>1</v>
+      </c>
+      <c r="N15" t="s">
+        <v>15</v>
+      </c>
+      <c r="O15" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P15" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>12</v>
+      </c>
+      <c r="R15" t="s">
+        <v>13</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="s">
+        <v>16</v>
+      </c>
+      <c r="U15" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0</v>
+      </c>
+      <c r="E16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" t="b">
+        <v>0</v>
+      </c>
+      <c r="H16" t="s">
+        <v>14</v>
+      </c>
+      <c r="I16" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" s="2">
+        <v>0</v>
+      </c>
+      <c r="K16" t="s">
+        <v>9</v>
+      </c>
+      <c r="L16" t="s">
+        <v>13</v>
+      </c>
+      <c r="M16" t="b">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>15</v>
+      </c>
+      <c r="O16" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P16" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>9</v>
+      </c>
+      <c r="R16" t="s">
+        <v>13</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="s">
+        <v>16</v>
+      </c>
+      <c r="U16" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0</v>
+      </c>
+      <c r="E17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I17" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" s="2">
+        <v>0</v>
+      </c>
+      <c r="K17" t="s">
+        <v>10</v>
+      </c>
+      <c r="L17" t="s">
+        <v>13</v>
+      </c>
+      <c r="M17" t="b">
+        <v>1</v>
+      </c>
+      <c r="N17" t="s">
+        <v>15</v>
+      </c>
+      <c r="O17" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P17" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>10</v>
+      </c>
+      <c r="R17" t="s">
+        <v>13</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="s">
+        <v>16</v>
+      </c>
+      <c r="U17" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C18" t="s">
+        <v>6</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0</v>
+      </c>
+      <c r="E18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" t="s">
+        <v>14</v>
+      </c>
+      <c r="I18" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" s="2">
+        <v>0</v>
+      </c>
+      <c r="K18" t="s">
+        <v>11</v>
+      </c>
+      <c r="L18" t="s">
+        <v>13</v>
+      </c>
+      <c r="M18" t="b">
+        <v>1</v>
+      </c>
+      <c r="N18" t="s">
+        <v>15</v>
+      </c>
+      <c r="O18" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P18" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>11</v>
+      </c>
+      <c r="R18" t="s">
+        <v>13</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="s">
+        <v>16</v>
+      </c>
+      <c r="U18" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C19" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="2">
+        <v>0</v>
+      </c>
+      <c r="E19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" t="b">
+        <v>1</v>
+      </c>
+      <c r="H19" t="s">
+        <v>14</v>
+      </c>
+      <c r="I19" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" s="2">
+        <v>0</v>
+      </c>
+      <c r="K19" t="s">
+        <v>12</v>
+      </c>
+      <c r="L19" t="s">
+        <v>13</v>
+      </c>
+      <c r="M19" t="b">
+        <v>1</v>
+      </c>
+      <c r="N19" t="s">
+        <v>15</v>
+      </c>
+      <c r="O19" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P19" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>12</v>
+      </c>
+      <c r="R19" t="s">
+        <v>13</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="s">
+        <v>16</v>
+      </c>
+      <c r="U19" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C20" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="2">
+        <v>10</v>
+      </c>
+      <c r="E20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" t="s">
+        <v>14</v>
+      </c>
+      <c r="I20" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" s="2">
+        <v>10</v>
+      </c>
+      <c r="K20" t="s">
+        <v>9</v>
+      </c>
+      <c r="L20" t="s">
+        <v>13</v>
+      </c>
+      <c r="M20" t="b">
+        <v>0</v>
+      </c>
+      <c r="N20" t="s">
+        <v>15</v>
+      </c>
+      <c r="O20" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P20" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>9</v>
+      </c>
+      <c r="R20" t="s">
+        <v>13</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="s">
+        <v>16</v>
+      </c>
+      <c r="U20" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C21" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" s="2">
+        <v>10</v>
+      </c>
+      <c r="E21" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" t="b">
+        <v>1</v>
+      </c>
+      <c r="H21" t="s">
+        <v>14</v>
+      </c>
+      <c r="I21" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" s="2">
+        <v>10</v>
+      </c>
+      <c r="K21" t="s">
+        <v>10</v>
+      </c>
+      <c r="L21" t="s">
+        <v>13</v>
+      </c>
+      <c r="M21" t="b">
+        <v>1</v>
+      </c>
+      <c r="N21" t="s">
+        <v>15</v>
+      </c>
+      <c r="O21" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P21" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>10</v>
+      </c>
+      <c r="R21" t="s">
+        <v>13</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="s">
+        <v>16</v>
+      </c>
+      <c r="U21" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C22" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22" s="2">
+        <v>10</v>
+      </c>
+      <c r="E22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" t="b">
+        <v>1</v>
+      </c>
+      <c r="H22" t="s">
+        <v>14</v>
+      </c>
+      <c r="I22" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" s="2">
+        <v>10</v>
+      </c>
+      <c r="K22" t="s">
+        <v>11</v>
+      </c>
+      <c r="L22" t="s">
+        <v>13</v>
+      </c>
+      <c r="M22" t="b">
+        <v>1</v>
+      </c>
+      <c r="N22" t="s">
+        <v>15</v>
+      </c>
+      <c r="O22" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P22" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>11</v>
+      </c>
+      <c r="R22" t="s">
+        <v>13</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="s">
+        <v>16</v>
+      </c>
+      <c r="U22" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C23" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" s="2">
+        <v>10</v>
+      </c>
+      <c r="E23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" t="b">
+        <v>1</v>
+      </c>
+      <c r="H23" t="s">
+        <v>14</v>
+      </c>
+      <c r="I23" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23" s="2">
+        <v>10</v>
+      </c>
+      <c r="K23" t="s">
+        <v>12</v>
+      </c>
+      <c r="L23" t="s">
+        <v>13</v>
+      </c>
+      <c r="M23" t="b">
+        <v>1</v>
+      </c>
+      <c r="N23" t="s">
+        <v>15</v>
+      </c>
+      <c r="O23" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P23" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>12</v>
+      </c>
+      <c r="R23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="s">
+        <v>16</v>
+      </c>
+      <c r="U23" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C24" t="s">
+        <v>6</v>
+      </c>
+      <c r="D24" s="2">
+        <v>20</v>
+      </c>
+      <c r="E24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" t="s">
+        <v>13</v>
+      </c>
+      <c r="G24" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" t="s">
+        <v>14</v>
+      </c>
+      <c r="I24" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24" s="2">
+        <v>20</v>
+      </c>
+      <c r="K24" t="s">
+        <v>9</v>
+      </c>
+      <c r="L24" t="s">
+        <v>13</v>
+      </c>
+      <c r="M24" t="b">
+        <v>0</v>
+      </c>
+      <c r="N24" t="s">
+        <v>15</v>
+      </c>
+      <c r="O24" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P24" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>9</v>
+      </c>
+      <c r="R24" t="s">
+        <v>13</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="s">
+        <v>16</v>
+      </c>
+      <c r="U24" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25" s="2">
+        <v>20</v>
+      </c>
+      <c r="E25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" t="s">
+        <v>13</v>
+      </c>
+      <c r="G25" t="b">
+        <v>1</v>
+      </c>
+      <c r="H25" t="s">
+        <v>14</v>
+      </c>
+      <c r="I25" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J25" s="2">
+        <v>20</v>
+      </c>
+      <c r="K25" t="s">
+        <v>10</v>
+      </c>
+      <c r="L25" t="s">
+        <v>13</v>
+      </c>
+      <c r="M25" t="b">
+        <v>1</v>
+      </c>
+      <c r="N25" t="s">
+        <v>15</v>
+      </c>
+      <c r="O25" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P25" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>10</v>
+      </c>
+      <c r="R25" t="s">
+        <v>13</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="s">
+        <v>16</v>
+      </c>
+      <c r="U25" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C26" t="s">
+        <v>6</v>
+      </c>
+      <c r="D26" s="2">
+        <v>20</v>
+      </c>
+      <c r="E26" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" t="s">
+        <v>13</v>
+      </c>
+      <c r="G26" t="b">
+        <v>1</v>
+      </c>
+      <c r="H26" t="s">
+        <v>14</v>
+      </c>
+      <c r="I26" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J26" s="2">
+        <v>20</v>
+      </c>
+      <c r="K26" t="s">
+        <v>11</v>
+      </c>
+      <c r="L26" t="s">
+        <v>13</v>
+      </c>
+      <c r="M26" t="b">
+        <v>1</v>
+      </c>
+      <c r="N26" t="s">
+        <v>15</v>
+      </c>
+      <c r="O26" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P26" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>11</v>
+      </c>
+      <c r="R26" t="s">
+        <v>13</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="s">
+        <v>16</v>
+      </c>
+      <c r="U26" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C27" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="2">
+        <v>20</v>
+      </c>
+      <c r="E27" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27" t="b">
+        <v>1</v>
+      </c>
+      <c r="H27" t="s">
+        <v>14</v>
+      </c>
+      <c r="I27" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J27" s="2">
+        <v>20</v>
+      </c>
+      <c r="K27" t="s">
+        <v>12</v>
+      </c>
+      <c r="L27" t="s">
+        <v>13</v>
+      </c>
+      <c r="M27" t="b">
+        <v>1</v>
+      </c>
+      <c r="N27" t="s">
+        <v>15</v>
+      </c>
+      <c r="O27" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P27" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>12</v>
+      </c>
+      <c r="R27" t="s">
+        <v>13</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="s">
+        <v>16</v>
+      </c>
+      <c r="U27" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C29" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K29" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L29" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="P29"/>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C30" t="s">
+        <v>2</v>
+      </c>
+      <c r="D30" s="2">
+        <v>0</v>
+      </c>
+      <c r="E30" t="s">
+        <v>14</v>
+      </c>
+      <c r="F30" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G30" s="2">
+        <v>0</v>
+      </c>
+      <c r="H30" t="s">
+        <v>15</v>
+      </c>
+      <c r="I30" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J30" s="2">
+        <v>0</v>
+      </c>
+      <c r="K30" t="s">
+        <v>16</v>
+      </c>
+      <c r="L30" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P30"/>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C31" t="s">
+        <v>2</v>
+      </c>
+      <c r="D31" s="2">
+        <v>10</v>
+      </c>
+      <c r="E31" t="s">
+        <v>14</v>
+      </c>
+      <c r="F31" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G31" s="2">
+        <v>10</v>
+      </c>
+      <c r="H31" t="s">
+        <v>15</v>
+      </c>
+      <c r="I31" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J31" s="2">
+        <v>10</v>
+      </c>
+      <c r="K31" t="s">
+        <v>16</v>
+      </c>
+      <c r="L31" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P31"/>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C32" t="s">
+        <v>2</v>
+      </c>
+      <c r="D32" s="2">
+        <v>20</v>
+      </c>
+      <c r="E32" t="s">
+        <v>14</v>
+      </c>
+      <c r="F32" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G32" s="2">
+        <v>20</v>
+      </c>
+      <c r="H32" t="s">
+        <v>15</v>
+      </c>
+      <c r="I32" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J32" s="2">
+        <v>20</v>
+      </c>
+      <c r="K32" t="s">
+        <v>16</v>
+      </c>
+      <c r="L32" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P32"/>
+    </row>
+    <row r="33" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C33" t="s">
+        <v>5</v>
+      </c>
+      <c r="D33" s="2">
+        <v>0</v>
+      </c>
+      <c r="E33" t="s">
+        <v>14</v>
+      </c>
+      <c r="F33" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G33" s="2">
+        <v>0</v>
+      </c>
+      <c r="H33" t="s">
+        <v>15</v>
+      </c>
+      <c r="I33" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J33" s="2">
+        <v>0</v>
+      </c>
+      <c r="K33" t="s">
+        <v>16</v>
+      </c>
+      <c r="L33" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P33"/>
+    </row>
+    <row r="34" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C34" t="s">
+        <v>5</v>
+      </c>
+      <c r="D34" s="2">
+        <v>10</v>
+      </c>
+      <c r="E34" t="s">
+        <v>14</v>
+      </c>
+      <c r="F34" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G34" s="2">
+        <v>10</v>
+      </c>
+      <c r="H34" t="s">
+        <v>15</v>
+      </c>
+      <c r="I34" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J34" s="2">
+        <v>10</v>
+      </c>
+      <c r="K34" t="s">
+        <v>16</v>
+      </c>
+      <c r="L34" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P34"/>
+    </row>
+    <row r="35" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C35" t="s">
+        <v>5</v>
+      </c>
+      <c r="D35" s="2">
+        <v>20</v>
+      </c>
+      <c r="E35" t="s">
+        <v>14</v>
+      </c>
+      <c r="F35" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G35" s="2">
+        <v>20</v>
+      </c>
+      <c r="H35" t="s">
+        <v>15</v>
+      </c>
+      <c r="I35" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J35" s="2">
+        <v>20</v>
+      </c>
+      <c r="K35" t="s">
+        <v>16</v>
+      </c>
+      <c r="L35" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P35"/>
+    </row>
+    <row r="37" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C37" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="38" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C38" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C40" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C41" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C42" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C43" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>